--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/9.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/9.xlsx
@@ -426,13 +426,13 @@
         <v>-12.69771880839719</v>
       </c>
       <c r="E2">
-        <v>-7.55016829310612</v>
+        <v>-6.237485947080691</v>
       </c>
       <c r="F2">
-        <v>-4.368159561200903</v>
+        <v>-4.021159769637801</v>
       </c>
       <c r="G2">
-        <v>-8.914846743186761</v>
+        <v>-9.814523909484638</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.43528478243985</v>
       </c>
       <c r="E3">
-        <v>-6.994547174735006</v>
+        <v>-7.389955411188751</v>
       </c>
       <c r="F3">
-        <v>-4.237214555635968</v>
+        <v>-3.92225270174354</v>
       </c>
       <c r="G3">
-        <v>-9.198494284991515</v>
+        <v>-9.686008531650129</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.51551015994072</v>
       </c>
       <c r="E4">
-        <v>-9.993361532776417</v>
+        <v>-6.535264812403071</v>
       </c>
       <c r="F4">
-        <v>-4.779099375851293</v>
+        <v>-3.467837680692023</v>
       </c>
       <c r="G4">
-        <v>-9.081102340168959</v>
+        <v>-9.416679099302723</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.80914276195821</v>
       </c>
       <c r="E5">
-        <v>-8.258380871639694</v>
+        <v>-7.764473797045112</v>
       </c>
       <c r="F5">
-        <v>-4.285098333354793</v>
+        <v>-3.686008945404343</v>
       </c>
       <c r="G5">
-        <v>-8.472074519491397</v>
+        <v>-8.775903146903548</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.25541696961761</v>
       </c>
       <c r="E6">
-        <v>-9.648187658489759</v>
+        <v>-9.362594916722021</v>
       </c>
       <c r="F6">
-        <v>-4.515310746634207</v>
+        <v>-3.433498538376373</v>
       </c>
       <c r="G6">
-        <v>-8.867327172516061</v>
+        <v>-9.291467645916407</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.7545782990895</v>
       </c>
       <c r="E7">
-        <v>-9.541333785804769</v>
+        <v>-10.10420951953617</v>
       </c>
       <c r="F7">
-        <v>-3.863523937987264</v>
+        <v>-3.315486833071347</v>
       </c>
       <c r="G7">
-        <v>-8.381554272811105</v>
+        <v>-9.504891895742142</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.21231637172229</v>
       </c>
       <c r="E8">
-        <v>-10.93560111955239</v>
+        <v>-9.867492597733218</v>
       </c>
       <c r="F8">
-        <v>-3.81097148158626</v>
+        <v>-3.525752159291348</v>
       </c>
       <c r="G8">
-        <v>-8.637091972441908</v>
+        <v>-9.160972561849416</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.51365281626691</v>
       </c>
       <c r="E9">
-        <v>-10.57321904403658</v>
+        <v>-10.9497797716704</v>
       </c>
       <c r="F9">
-        <v>-3.852370799275971</v>
+        <v>-3.124245792624039</v>
       </c>
       <c r="G9">
-        <v>-8.126811104109725</v>
+        <v>-9.406221085944164</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-22.57052697729356</v>
       </c>
       <c r="E10">
-        <v>-11.65379898327288</v>
+        <v>-11.8337650688117</v>
       </c>
       <c r="F10">
-        <v>-3.955174507433001</v>
+        <v>-2.855023901611991</v>
       </c>
       <c r="G10">
-        <v>-8.054922607724452</v>
+        <v>-9.707642946749267</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-23.30908506477628</v>
       </c>
       <c r="E11">
-        <v>-13.5964192346093</v>
+        <v>-12.28409463803047</v>
       </c>
       <c r="F11">
-        <v>-3.871230239935507</v>
+        <v>-2.697007020956166</v>
       </c>
       <c r="G11">
-        <v>-9.044365216319667</v>
+        <v>-9.701945497876181</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-23.6748236857844</v>
       </c>
       <c r="E12">
-        <v>-13.98447322927459</v>
+        <v>-13.19151478816147</v>
       </c>
       <c r="F12">
-        <v>-2.958084403663889</v>
+        <v>-2.382184332787408</v>
       </c>
       <c r="G12">
-        <v>-7.821426520294116</v>
+        <v>-8.711926854357133</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-23.63348869724579</v>
       </c>
       <c r="E13">
-        <v>-13.64351536428907</v>
+        <v>-14.18253509694807</v>
       </c>
       <c r="F13">
-        <v>-3.367881899665818</v>
+        <v>-2.207148643841067</v>
       </c>
       <c r="G13">
-        <v>-8.022571956714694</v>
+        <v>-8.883436287110156</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-23.18757683748544</v>
       </c>
       <c r="E14">
-        <v>-14.80990988597072</v>
+        <v>-15.28281389811772</v>
       </c>
       <c r="F14">
-        <v>-3.231095247176342</v>
+        <v>-1.789546270169961</v>
       </c>
       <c r="G14">
-        <v>-6.695592746026467</v>
+        <v>-8.445729198089877</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-22.35724228042704</v>
       </c>
       <c r="E15">
-        <v>-14.91584900690616</v>
+        <v>-15.46974024820634</v>
       </c>
       <c r="F15">
-        <v>-2.727450351376451</v>
+        <v>-1.937523337903856</v>
       </c>
       <c r="G15">
-        <v>-7.245755756470249</v>
+        <v>-7.745889802724565</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-21.18116868502423</v>
       </c>
       <c r="E16">
-        <v>-17.09072563314798</v>
+        <v>-16.31898309276079</v>
       </c>
       <c r="F16">
-        <v>-2.421786093213044</v>
+        <v>-1.398857553415811</v>
       </c>
       <c r="G16">
-        <v>-5.933826285803549</v>
+        <v>-7.803701859476858</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-19.73110768442244</v>
       </c>
       <c r="E17">
-        <v>-16.46403011522647</v>
+        <v>-17.49244656236841</v>
       </c>
       <c r="F17">
-        <v>-2.144596136153468</v>
+        <v>-1.419584134201257</v>
       </c>
       <c r="G17">
-        <v>-6.094791631013993</v>
+        <v>-6.995346091879776</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-18.09598398668068</v>
       </c>
       <c r="E18">
-        <v>-17.26021282983305</v>
+        <v>-18.47026184094864</v>
       </c>
       <c r="F18">
-        <v>-1.810316754427756</v>
+        <v>-0.8883421783771004</v>
       </c>
       <c r="G18">
-        <v>-5.727218449243173</v>
+        <v>-7.145939497915683</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.36795233655317</v>
       </c>
       <c r="E19">
-        <v>-18.10001833455552</v>
+        <v>-19.1784019638981</v>
       </c>
       <c r="F19">
-        <v>-1.4273492502351</v>
+        <v>-0.4470294445356637</v>
       </c>
       <c r="G19">
-        <v>-4.995402494514042</v>
+        <v>-6.548399270259392</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.65093976866938</v>
       </c>
       <c r="E20">
-        <v>-19.87902934846882</v>
+        <v>-19.55999382615444</v>
       </c>
       <c r="F20">
-        <v>-1.307959969939218</v>
+        <v>-0.2008452793628731</v>
       </c>
       <c r="G20">
-        <v>-4.895420708682512</v>
+        <v>-6.402996799629062</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.04894357213752</v>
       </c>
       <c r="E21">
-        <v>-19.46732313406147</v>
+        <v>-20.51960916769784</v>
       </c>
       <c r="F21">
-        <v>-1.271925159550037</v>
+        <v>-0.0905672121303833</v>
       </c>
       <c r="G21">
-        <v>-5.0847143920725</v>
+        <v>-6.226329536925855</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.64540315231692</v>
       </c>
       <c r="E22">
-        <v>-21.07304303312325</v>
+        <v>-21.06725111486744</v>
       </c>
       <c r="F22">
-        <v>-1.234342958852426</v>
+        <v>0.7910054005835317</v>
       </c>
       <c r="G22">
-        <v>-4.798415103290789</v>
+        <v>-5.79545872444417</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.5048276998355</v>
       </c>
       <c r="E23">
-        <v>-21.66720146529964</v>
+        <v>-22.18332523337585</v>
       </c>
       <c r="F23">
-        <v>-1.145339851626036</v>
+        <v>0.3195848251199443</v>
       </c>
       <c r="G23">
-        <v>-4.295546546421035</v>
+        <v>-5.757460282744415</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.681271247809729</v>
       </c>
       <c r="E24">
-        <v>-22.13151043378009</v>
+        <v>-22.62817987751935</v>
       </c>
       <c r="F24">
-        <v>-0.3302694023762678</v>
+        <v>0.9815199628185844</v>
       </c>
       <c r="G24">
-        <v>-5.320385507922137</v>
+        <v>-5.539063593518695</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.190819355429854</v>
       </c>
       <c r="E25">
-        <v>-22.12727178210891</v>
+        <v>-22.63444728554597</v>
       </c>
       <c r="F25">
-        <v>-0.1284211173361123</v>
+        <v>0.6855078416325979</v>
       </c>
       <c r="G25">
-        <v>-5.586682480555572</v>
+        <v>-6.148925671672155</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.014934570197111</v>
       </c>
       <c r="E26">
-        <v>-21.92102696190357</v>
+        <v>-22.67488655843446</v>
       </c>
       <c r="F26">
-        <v>0.0714548249179776</v>
+        <v>0.6708142606417403</v>
       </c>
       <c r="G26">
-        <v>-4.942801236440562</v>
+        <v>-5.865615805512405</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.133870795601183</v>
       </c>
       <c r="E27">
-        <v>-23.08610369764898</v>
+        <v>-23.51194327943427</v>
       </c>
       <c r="F27">
-        <v>0.06212989306466356</v>
+        <v>0.9940912665234698</v>
       </c>
       <c r="G27">
-        <v>-6.198789108584657</v>
+        <v>-5.94445313698461</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.500192398383618</v>
       </c>
       <c r="E28">
-        <v>-22.47355966100145</v>
+        <v>-23.50457545222379</v>
       </c>
       <c r="F28">
-        <v>-0.0691124963978761</v>
+        <v>0.7836494980466722</v>
       </c>
       <c r="G28">
-        <v>-6.327863968615302</v>
+        <v>-5.490113867175031</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.04919022073511</v>
       </c>
       <c r="E29">
-        <v>-22.71403974470478</v>
+        <v>-22.99696974375601</v>
       </c>
       <c r="F29">
-        <v>-0.09521766672969972</v>
+        <v>0.7305378936487791</v>
       </c>
       <c r="G29">
-        <v>-5.498807359761158</v>
+        <v>-6.659961344387291</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.73027697888574</v>
       </c>
       <c r="E30">
-        <v>-22.70501449600749</v>
+        <v>-22.74574359123248</v>
       </c>
       <c r="F30">
-        <v>-0.455617957767889</v>
+        <v>0.8827404635043546</v>
       </c>
       <c r="G30">
-        <v>-6.070581611485302</v>
+        <v>-6.477563527355605</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.4899961316493</v>
       </c>
       <c r="E31">
-        <v>-21.51234576813334</v>
+        <v>-22.6493459650312</v>
       </c>
       <c r="F31">
-        <v>-0.07936105790531159</v>
+        <v>0.640476961249014</v>
       </c>
       <c r="G31">
-        <v>-5.407095316686728</v>
+        <v>-6.572450383602196</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.27332611726893</v>
       </c>
       <c r="E32">
-        <v>-22.7089723822902</v>
+        <v>-23.47959186112348</v>
       </c>
       <c r="F32">
-        <v>-0.3950427630707724</v>
+        <v>0.6174491758185905</v>
       </c>
       <c r="G32">
-        <v>-5.769196166681132</v>
+        <v>-6.599808731938734</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.04894316684159</v>
       </c>
       <c r="E33">
-        <v>-22.17572192551697</v>
+        <v>-22.03617699897061</v>
       </c>
       <c r="F33">
-        <v>-0.1796183646661358</v>
+        <v>0.6846753323927844</v>
       </c>
       <c r="G33">
-        <v>-6.385950800647354</v>
+        <v>-6.878189195790508</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.79227336593988</v>
       </c>
       <c r="E34">
-        <v>-20.49990124881646</v>
+        <v>-21.93730229748714</v>
       </c>
       <c r="F34">
-        <v>-0.7541549427976084</v>
+        <v>0.6604281901454401</v>
       </c>
       <c r="G34">
-        <v>-6.177333462944641</v>
+        <v>-5.982825670330302</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.47903411853405</v>
       </c>
       <c r="E35">
-        <v>-21.14848288161703</v>
+        <v>-21.61269675214332</v>
       </c>
       <c r="F35">
-        <v>-0.1127931379148968</v>
+        <v>0.7052395531672822</v>
       </c>
       <c r="G35">
-        <v>-5.884181344896638</v>
+        <v>-6.854038766081525</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.09783774581215</v>
       </c>
       <c r="E36">
-        <v>-20.73769594743324</v>
+        <v>-20.88674161244769</v>
       </c>
       <c r="F36">
-        <v>-0.01005072894567415</v>
+        <v>0.6014757671904076</v>
       </c>
       <c r="G36">
-        <v>-5.89825447398408</v>
+        <v>-6.699949423956148</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.64719533011899</v>
       </c>
       <c r="E37">
-        <v>-21.08127579886919</v>
+        <v>-20.66663513330487</v>
       </c>
       <c r="F37">
-        <v>-0.667173880401452</v>
+        <v>0.7087336068722905</v>
       </c>
       <c r="G37">
-        <v>-5.533528361377034</v>
+        <v>-6.545293978543555</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-16.12148746268697</v>
       </c>
       <c r="E38">
-        <v>-19.5623893889045</v>
+        <v>-20.24610745153058</v>
       </c>
       <c r="F38">
-        <v>-0.01504909785416637</v>
+        <v>0.5738579979810722</v>
       </c>
       <c r="G38">
-        <v>-6.072988378092353</v>
+        <v>-5.85519420815478</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-16.51508918930749</v>
       </c>
       <c r="E39">
-        <v>-19.05198055502596</v>
+        <v>-19.69785868884395</v>
       </c>
       <c r="F39">
-        <v>0.04323980281122364</v>
+        <v>0.286962888430297</v>
       </c>
       <c r="G39">
-        <v>-5.99868649400895</v>
+        <v>-4.938653122879855</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-16.83236648052582</v>
       </c>
       <c r="E40">
-        <v>-18.87930984111349</v>
+        <v>-19.06868156716625</v>
       </c>
       <c r="F40">
-        <v>-0.3221215806023319</v>
+        <v>0.2660341859985675</v>
       </c>
       <c r="G40">
-        <v>-5.37910465415219</v>
+        <v>-5.533425734465316</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.06905379747101</v>
       </c>
       <c r="E41">
-        <v>-18.41245587024073</v>
+        <v>-19.38407166790446</v>
       </c>
       <c r="F41">
-        <v>-0.3074520222661555</v>
+        <v>0.5419020686832756</v>
       </c>
       <c r="G41">
-        <v>-4.535392260195692</v>
+        <v>-5.22970635505596</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.21376022266966</v>
       </c>
       <c r="E42">
-        <v>-16.31074127006683</v>
+        <v>-18.50456050308274</v>
       </c>
       <c r="F42">
-        <v>-0.6444931809128015</v>
+        <v>0.1627284871954411</v>
       </c>
       <c r="G42">
-        <v>-4.989993063102872</v>
+        <v>-5.329896705256464</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.26612791145939</v>
       </c>
       <c r="E43">
-        <v>-16.49880426713138</v>
+        <v>-17.92966167086097</v>
       </c>
       <c r="F43">
-        <v>-0.7284515306561425</v>
+        <v>0.4883075260895504</v>
       </c>
       <c r="G43">
-        <v>-5.0236646217828</v>
+        <v>-5.341536583372541</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-17.22172685804495</v>
       </c>
       <c r="E44">
-        <v>-17.67632072097586</v>
+        <v>-17.61371909629382</v>
       </c>
       <c r="F44">
-        <v>-0.2910230115664328</v>
+        <v>0.3245119544317958</v>
       </c>
       <c r="G44">
-        <v>-4.593419502408038</v>
+        <v>-5.167107249453881</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-17.0701785438321</v>
       </c>
       <c r="E45">
-        <v>-16.22701884261302</v>
+        <v>-15.77082489955432</v>
       </c>
       <c r="F45">
-        <v>-1.0159331243281</v>
+        <v>0.2015399851188064</v>
       </c>
       <c r="G45">
-        <v>-4.783262736357544</v>
+        <v>-5.04397150812069</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-16.81254716482519</v>
       </c>
       <c r="E46">
-        <v>-16.77503665312526</v>
+        <v>-16.12342094273955</v>
       </c>
       <c r="F46">
-        <v>-1.101573888266527</v>
+        <v>-0.03709029770785562</v>
       </c>
       <c r="G46">
-        <v>-4.868472867992845</v>
+        <v>-4.901671018660656</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-16.4571308097112</v>
       </c>
       <c r="E47">
-        <v>-16.16810339577323</v>
+        <v>-16.22740829137769</v>
       </c>
       <c r="F47">
-        <v>-0.9410967564243868</v>
+        <v>-0.3211938091111964</v>
       </c>
       <c r="G47">
-        <v>-5.306696402117251</v>
+        <v>-5.175645146399662</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-16.01103741573422</v>
       </c>
       <c r="E48">
-        <v>-14.54311936828282</v>
+        <v>-14.53946036128463</v>
       </c>
       <c r="F48">
-        <v>-1.03603345935703</v>
+        <v>-0.4934718629736181</v>
       </c>
       <c r="G48">
-        <v>-5.157235202655775</v>
+        <v>-4.140606394092064</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.48695092677585</v>
       </c>
       <c r="E49">
-        <v>-13.87440866851816</v>
+        <v>-14.98981257287344</v>
       </c>
       <c r="F49">
-        <v>-1.28003653315825</v>
+        <v>-0.5268931742069669</v>
       </c>
       <c r="G49">
-        <v>-4.459375513522947</v>
+        <v>-4.79109217655792</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.91356318918451</v>
       </c>
       <c r="E50">
-        <v>-12.98574998620094</v>
+        <v>-13.52136430640617</v>
       </c>
       <c r="F50">
-        <v>-1.550616118343485</v>
+        <v>-0.437653982270779</v>
       </c>
       <c r="G50">
-        <v>-4.863477254774085</v>
+        <v>-4.517190880820779</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.3173479261362</v>
       </c>
       <c r="E51">
-        <v>-13.71724344960795</v>
+        <v>-14.03982023859633</v>
       </c>
       <c r="F51">
-        <v>-1.507575804828829</v>
+        <v>-0.7808507390876281</v>
       </c>
       <c r="G51">
-        <v>-3.882271283480577</v>
+        <v>-4.472909023687488</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.72341656019973</v>
       </c>
       <c r="E52">
-        <v>-12.46386599918697</v>
+        <v>-13.41093293925512</v>
       </c>
       <c r="F52">
-        <v>-1.374151495627315</v>
+        <v>-0.5231622074247579</v>
       </c>
       <c r="G52">
-        <v>-3.721706514280385</v>
+        <v>-4.380498455504272</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.17466082201102</v>
       </c>
       <c r="E53">
-        <v>-12.67101198571984</v>
+        <v>-12.28281760836031</v>
       </c>
       <c r="F53">
-        <v>-1.501809539337941</v>
+        <v>-0.6049883394732931</v>
       </c>
       <c r="G53">
-        <v>-4.517296818278036</v>
+        <v>-4.64714303541933</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.70538049468158</v>
       </c>
       <c r="E54">
-        <v>-12.60977343171411</v>
+        <v>-12.67726580832443</v>
       </c>
       <c r="F54">
-        <v>-1.212569321669841</v>
+        <v>-0.8927051894876453</v>
       </c>
       <c r="G54">
-        <v>-3.978770375404792</v>
+        <v>-4.802152709204625</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.33668979995989</v>
       </c>
       <c r="E55">
-        <v>-10.49220464403936</v>
+        <v>-11.79233858858954</v>
       </c>
       <c r="F55">
-        <v>-1.924650508464352</v>
+        <v>-0.7195590065870899</v>
       </c>
       <c r="G55">
-        <v>-5.397292791344946</v>
+        <v>-5.204354197316222</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.09716801494123</v>
       </c>
       <c r="E56">
-        <v>-11.638519911971</v>
+        <v>-11.78052379990352</v>
       </c>
       <c r="F56">
-        <v>-1.767889432791171</v>
+        <v>-1.049681640685554</v>
       </c>
       <c r="G56">
-        <v>-5.505934964307209</v>
+        <v>-4.965061344646621</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.00275637696838</v>
       </c>
       <c r="E57">
-        <v>-10.19261438911391</v>
+        <v>-10.22880595338321</v>
       </c>
       <c r="F57">
-        <v>-1.90816848225085</v>
+        <v>-1.185799800680972</v>
       </c>
       <c r="G57">
-        <v>-5.069727552416219</v>
+        <v>-5.102842939445549</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.05024177533624</v>
       </c>
       <c r="E58">
-        <v>-10.15941614616368</v>
+        <v>-10.52265863174094</v>
       </c>
       <c r="F58">
-        <v>-1.435669372428818</v>
+        <v>-1.162897098728371</v>
       </c>
       <c r="G58">
-        <v>-5.43111663511968</v>
+        <v>-5.044673343775015</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.23783130045862</v>
       </c>
       <c r="E59">
-        <v>-9.333336446158462</v>
+        <v>-9.668158228863586</v>
       </c>
       <c r="F59">
-        <v>-1.437425511322753</v>
+        <v>-0.9825010443185146</v>
       </c>
       <c r="G59">
-        <v>-5.322904833077523</v>
+        <v>-4.808740694827775</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.55711036725447</v>
       </c>
       <c r="E60">
-        <v>-8.618050391224905</v>
+        <v>-9.924080408933067</v>
       </c>
       <c r="F60">
-        <v>-1.879392655412401</v>
+        <v>-1.265699978517998</v>
       </c>
       <c r="G60">
-        <v>-4.698532633825438</v>
+        <v>-4.956513516064224</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.98396272651959</v>
       </c>
       <c r="E61">
-        <v>-9.241879385099551</v>
+        <v>-9.502656089305257</v>
       </c>
       <c r="F61">
-        <v>-1.924107927815518</v>
+        <v>-1.266443852445712</v>
       </c>
       <c r="G61">
-        <v>-4.960138563429725</v>
+        <v>-5.426995005923287</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.49276860740746</v>
       </c>
       <c r="E62">
-        <v>-7.993650809625294</v>
+        <v>-8.718668555201333</v>
       </c>
       <c r="F62">
-        <v>-1.629581069382751</v>
+        <v>-1.325465029895177</v>
       </c>
       <c r="G62">
-        <v>-4.249692180156589</v>
+        <v>-5.331757231849534</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.06508393944399</v>
       </c>
       <c r="E63">
-        <v>-9.940559525846981</v>
+        <v>-9.52374066428497</v>
       </c>
       <c r="F63">
-        <v>-1.983001536684952</v>
+        <v>-1.312759530671038</v>
       </c>
       <c r="G63">
-        <v>-6.135964885885908</v>
+        <v>-6.055127984907984</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.67056387941063</v>
       </c>
       <c r="E64">
-        <v>-9.453404405997833</v>
+        <v>-8.779250480475948</v>
       </c>
       <c r="F64">
-        <v>-2.122450562007026</v>
+        <v>-1.348493643693003</v>
       </c>
       <c r="G64">
-        <v>-6.225376099810545</v>
+        <v>-6.189297774523567</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.27530079599917</v>
       </c>
       <c r="E65">
-        <v>-8.345513240021281</v>
+        <v>-8.561372010544904</v>
       </c>
       <c r="F65">
-        <v>-2.183429999996709</v>
+        <v>-1.510228237252593</v>
       </c>
       <c r="G65">
-        <v>-5.453932914976336</v>
+        <v>-6.052062419738619</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.85916979059466</v>
       </c>
       <c r="E66">
-        <v>-7.615903621801463</v>
+        <v>-8.717070003876627</v>
       </c>
       <c r="F66">
-        <v>-2.263582829891589</v>
+        <v>-1.572684654321467</v>
       </c>
       <c r="G66">
-        <v>-6.147968924011305</v>
+        <v>-6.008475777168575</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.39582791795816</v>
       </c>
       <c r="E67">
-        <v>-5.979553124551803</v>
+        <v>-8.104082176776343</v>
       </c>
       <c r="F67">
-        <v>-2.42829457589684</v>
+        <v>-1.258629034367702</v>
       </c>
       <c r="G67">
-        <v>-6.400381468653038</v>
+        <v>-6.429203078117932</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.85569451525159</v>
       </c>
       <c r="E68">
-        <v>-8.174871282464247</v>
+        <v>-9.022818983452506</v>
       </c>
       <c r="F68">
-        <v>-2.07800782247943</v>
+        <v>-1.036452613262846</v>
       </c>
       <c r="G68">
-        <v>-5.968090432135005</v>
+        <v>-6.528665108299796</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-17.23173701549445</v>
       </c>
       <c r="E69">
-        <v>-7.274112517598535</v>
+        <v>-7.535328483782985</v>
       </c>
       <c r="F69">
-        <v>-2.524675123212563</v>
+        <v>-1.882654766244625</v>
       </c>
       <c r="G69">
-        <v>-5.765806168048918</v>
+        <v>-6.452711261992297</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-17.51863449452487</v>
       </c>
       <c r="E70">
-        <v>-7.16172937815018</v>
+        <v>-7.121910506200734</v>
       </c>
       <c r="F70">
-        <v>-2.178222054135309</v>
+        <v>-1.392737575043928</v>
       </c>
       <c r="G70">
-        <v>-5.28589624449401</v>
+        <v>-6.286068331182003</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-17.70984892033048</v>
       </c>
       <c r="E71">
-        <v>-8.499345502061843</v>
+        <v>-7.761140840175467</v>
       </c>
       <c r="F71">
-        <v>-2.967469806337608</v>
+        <v>-2.117573134739343</v>
       </c>
       <c r="G71">
-        <v>-5.625266888815778</v>
+        <v>-6.053320427043542</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-17.81439103011283</v>
       </c>
       <c r="E72">
-        <v>-7.553800129260272</v>
+        <v>-7.671218931805157</v>
       </c>
       <c r="F72">
-        <v>-2.639208513793233</v>
+        <v>-1.646415151742443</v>
       </c>
       <c r="G72">
-        <v>-5.320868847570871</v>
+        <v>-5.647404506836884</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-17.84760072983766</v>
       </c>
       <c r="E73">
-        <v>-7.532086096393493</v>
+        <v>-7.84767544998804</v>
       </c>
       <c r="F73">
-        <v>-2.568865210682305</v>
+        <v>-1.808727117381783</v>
       </c>
       <c r="G73">
-        <v>-5.650807747651255</v>
+        <v>-5.620688404334966</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-17.82096859405155</v>
       </c>
       <c r="E74">
-        <v>-7.654794156579336</v>
+        <v>-7.414572195894447</v>
       </c>
       <c r="F74">
-        <v>-2.664432301208478</v>
+        <v>-1.775806968427128</v>
       </c>
       <c r="G74">
-        <v>-5.034400720966657</v>
+        <v>-5.344125429984251</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.74930617006425</v>
       </c>
       <c r="E75">
-        <v>-6.578398527326131</v>
+        <v>-8.855759048835539</v>
       </c>
       <c r="F75">
-        <v>-2.838051481896033</v>
+        <v>-1.909191515993307</v>
       </c>
       <c r="G75">
-        <v>-4.393032180915953</v>
+        <v>-5.390473067534048</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.65848454691742</v>
       </c>
       <c r="E76">
-        <v>-8.159334088143929</v>
+        <v>-8.126484537692289</v>
       </c>
       <c r="F76">
-        <v>-3.147208137029641</v>
+        <v>-2.279102293183038</v>
       </c>
       <c r="G76">
-        <v>-4.56188324560094</v>
+        <v>-4.836896884639277</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.56328256684692</v>
       </c>
       <c r="E77">
-        <v>-9.562640256010859</v>
+        <v>-8.177244202844266</v>
       </c>
       <c r="F77">
-        <v>-2.504448876338407</v>
+        <v>-2.123017993677944</v>
       </c>
       <c r="G77">
-        <v>-5.146601730383636</v>
+        <v>-4.481516442089593</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.47000598208965</v>
       </c>
       <c r="E78">
-        <v>-8.840307895521367</v>
+        <v>-9.211325770969799</v>
       </c>
       <c r="F78">
-        <v>-3.154804266113313</v>
+        <v>-2.270542772809911</v>
       </c>
       <c r="G78">
-        <v>-5.060166696898804</v>
+        <v>-3.906934847748147</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.39608670059723</v>
       </c>
       <c r="E79">
-        <v>-9.238360760795592</v>
+        <v>-9.723319570751018</v>
       </c>
       <c r="F79">
-        <v>-3.552925095205381</v>
+        <v>-2.446746459794199</v>
       </c>
       <c r="G79">
-        <v>-4.275736241914036</v>
+        <v>-4.170146391938981</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.34648180111081</v>
       </c>
       <c r="E80">
-        <v>-10.80268135047925</v>
+        <v>-10.30508809804242</v>
       </c>
       <c r="F80">
-        <v>-3.542880312079034</v>
+        <v>-2.400560835251113</v>
       </c>
       <c r="G80">
-        <v>-3.480248564828101</v>
+        <v>-3.890405293870566</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.31163401989165</v>
       </c>
       <c r="E81">
-        <v>-11.34644692389828</v>
+        <v>-10.99832954150664</v>
       </c>
       <c r="F81">
-        <v>-3.371103420495306</v>
+        <v>-2.516681377775547</v>
       </c>
       <c r="G81">
-        <v>-4.238485983506156</v>
+        <v>-3.323149936807527</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.29513355272409</v>
       </c>
       <c r="E82">
-        <v>-11.36145881523371</v>
+        <v>-11.254772496087</v>
       </c>
       <c r="F82">
-        <v>-3.434435421908939</v>
+        <v>-2.233745864410154</v>
       </c>
       <c r="G82">
-        <v>-1.953729532305843</v>
+        <v>-3.019142539936253</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-17.29445141026928</v>
       </c>
       <c r="E83">
-        <v>-13.57446519262011</v>
+        <v>-12.01612671710059</v>
       </c>
       <c r="F83">
-        <v>-3.558174459436921</v>
+        <v>-2.950160241088709</v>
       </c>
       <c r="G83">
-        <v>-2.429494652845583</v>
+        <v>-2.849659161053265</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-17.29638592270225</v>
       </c>
       <c r="E84">
-        <v>-13.13900713204253</v>
+        <v>-12.52615968763649</v>
       </c>
       <c r="F84">
-        <v>-3.490744524481638</v>
+        <v>-2.61161808070819</v>
       </c>
       <c r="G84">
-        <v>-2.937891820765921</v>
+        <v>-2.554865012417784</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-17.29670829258663</v>
       </c>
       <c r="E85">
-        <v>-14.04172672615356</v>
+        <v>-13.87182290985978</v>
       </c>
       <c r="F85">
-        <v>-3.713104843149915</v>
+        <v>-3.199314931767939</v>
       </c>
       <c r="G85">
-        <v>-3.370954214394602</v>
+        <v>-2.44486551578442</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.29774524060554</v>
       </c>
       <c r="E86">
-        <v>-15.62453707521054</v>
+        <v>-15.00017372140299</v>
       </c>
       <c r="F86">
-        <v>-4.153098816086096</v>
+        <v>-2.904371404531564</v>
       </c>
       <c r="G86">
-        <v>-3.014074094715629</v>
+        <v>-2.247494101278611</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.29336962532843</v>
       </c>
       <c r="E87">
-        <v>-18.19544233884515</v>
+        <v>-15.98970416224106</v>
       </c>
       <c r="F87">
-        <v>-3.806879346616431</v>
+        <v>-3.173826895151201</v>
       </c>
       <c r="G87">
-        <v>-2.757294940507599</v>
+        <v>-2.645752729652934</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.2774814741439</v>
       </c>
       <c r="E88">
-        <v>-17.60557237155403</v>
+        <v>-17.14955956745563</v>
       </c>
       <c r="F88">
-        <v>-4.020756354712637</v>
+        <v>-3.283598001533177</v>
       </c>
       <c r="G88">
-        <v>-3.056548393984478</v>
+        <v>-1.960933279399297</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.26106056659314</v>
       </c>
       <c r="E89">
-        <v>-19.42363241683547</v>
+        <v>-18.48243890755527</v>
       </c>
       <c r="F89">
-        <v>-4.391715845034312</v>
+        <v>-3.704155161730069</v>
       </c>
       <c r="G89">
-        <v>-2.841028568832385</v>
+        <v>-1.611088068991275</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.24766227260317</v>
       </c>
       <c r="E90">
-        <v>-20.81913149551317</v>
+        <v>-20.81158705781639</v>
       </c>
       <c r="F90">
-        <v>-4.213755190788686</v>
+        <v>-3.738718791611879</v>
       </c>
       <c r="G90">
-        <v>-2.709480731283905</v>
+        <v>-1.495520234760857</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.2377033954567</v>
       </c>
       <c r="E91">
-        <v>-22.68508921037374</v>
+        <v>-20.90225163592396</v>
       </c>
       <c r="F91">
-        <v>-4.480871371862817</v>
+        <v>-3.749523187646593</v>
       </c>
       <c r="G91">
-        <v>-2.496460368013961</v>
+        <v>-1.903045080099601</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.25114952219234</v>
       </c>
       <c r="E92">
-        <v>-24.73579507932524</v>
+        <v>-23.95081580941364</v>
       </c>
       <c r="F92">
-        <v>-5.134840100248735</v>
+        <v>-3.902134970999151</v>
       </c>
       <c r="G92">
-        <v>-2.872872706374634</v>
+        <v>-2.155010701093531</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.30123966330236</v>
       </c>
       <c r="E93">
-        <v>-27.20197938153248</v>
+        <v>-25.44595490168211</v>
       </c>
       <c r="F93">
-        <v>-4.960395037260589</v>
+        <v>-4.56261383880367</v>
       </c>
       <c r="G93">
-        <v>-2.702581554380064</v>
+        <v>-2.396654041096014</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.38804812794881</v>
       </c>
       <c r="E94">
-        <v>-28.26336311945026</v>
+        <v>-27.78103082441928</v>
       </c>
       <c r="F94">
-        <v>-5.666952670213234</v>
+        <v>-4.197885328085853</v>
       </c>
       <c r="G94">
-        <v>-3.575595586904651</v>
+        <v>-2.77368545147253</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.52568618233112</v>
       </c>
       <c r="E95">
-        <v>-30.70488535221173</v>
+        <v>-29.57425671824266</v>
       </c>
       <c r="F95">
-        <v>-4.818974497519853</v>
+        <v>-4.317021956323881</v>
       </c>
       <c r="G95">
-        <v>-3.052036120414452</v>
+        <v>-2.375314264549871</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.7207118201806</v>
       </c>
       <c r="E96">
-        <v>-33.6567416990306</v>
+        <v>-31.7515696635006</v>
       </c>
       <c r="F96">
-        <v>-5.17285553709801</v>
+        <v>-4.719678925313678</v>
       </c>
       <c r="G96">
-        <v>-4.158960058561783</v>
+        <v>-3.108447816403633</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.95978301163214</v>
       </c>
       <c r="E97">
-        <v>-34.95922365735375</v>
+        <v>-34.51600832080103</v>
       </c>
       <c r="F97">
-        <v>-5.286939952546363</v>
+        <v>-4.855706793262191</v>
       </c>
       <c r="G97">
-        <v>-4.174830813877049</v>
+        <v>-3.32812899729859</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.23999267603929</v>
       </c>
       <c r="E98">
-        <v>-38.48517050378402</v>
+        <v>-37.66018895872566</v>
       </c>
       <c r="F98">
-        <v>-5.539273088950135</v>
+        <v>-4.95162179809754</v>
       </c>
       <c r="G98">
-        <v>-5.59010227409764</v>
+        <v>-4.049652465946128</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.54708683779602</v>
       </c>
       <c r="E99">
-        <v>-40.29682728681861</v>
+        <v>-38.97598463063137</v>
       </c>
       <c r="F99">
-        <v>-6.189694748117264</v>
+        <v>-5.328129693283166</v>
       </c>
       <c r="G99">
-        <v>-5.353149977124304</v>
+        <v>-4.550918718774875</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.87441753076216</v>
       </c>
       <c r="E100">
-        <v>-42.72689474457768</v>
+        <v>-41.45595813619196</v>
       </c>
       <c r="F100">
-        <v>-6.073458234156438</v>
+        <v>-5.373170514075583</v>
       </c>
       <c r="G100">
-        <v>-5.097635451312275</v>
+        <v>-4.894950611215936</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.18205587857202</v>
       </c>
       <c r="E101">
-        <v>-45.65560379650634</v>
+        <v>-43.68351450056501</v>
       </c>
       <c r="F101">
-        <v>-5.998237503777826</v>
+        <v>-5.519214172291345</v>
       </c>
       <c r="G101">
-        <v>-5.611773105197709</v>
+        <v>-4.809578262849211</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-19.50095310452774</v>
       </c>
       <c r="E102">
-        <v>-47.5521921095548</v>
+        <v>-46.21211928849397</v>
       </c>
       <c r="F102">
-        <v>-6.127907651909852</v>
+        <v>-5.508671540355915</v>
       </c>
       <c r="G102">
-        <v>-6.869750615210906</v>
+        <v>-5.682827344107086</v>
       </c>
     </row>
   </sheetData>
